--- a/DateBase/orders/Nha Thu_2026-8-15.xlsx
+++ b/DateBase/orders/Nha Thu_2026-8-15.xlsx
@@ -766,6 +766,9 @@
       <c r="C41" t="str">
         <v>420_松虫草QQ糖_scabiosa white pink_undefined_1bunch</v>
       </c>
+      <c r="F41" t="str">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -824,7 +827,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>010510101055551010151010101051065510101520101010105555510101010100</v>
+        <v>010510101055551010151010101051065510101520101010105555510101010101</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-8-15.xlsx
+++ b/DateBase/orders/Nha Thu_2026-8-15.xlsx
@@ -767,7 +767,7 @@
         <v>420_松虫草QQ糖_scabiosa white pink_undefined_1bunch</v>
       </c>
       <c r="F41" t="str">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -827,7 +827,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>010510101055551010151010101051065510101520101010105555510101010101</v>
+        <v>0105101010555510101510101010510655101015201010101055555101010101010</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-8-15.xlsx
+++ b/DateBase/orders/Nha Thu_2026-8-15.xlsx
@@ -829,6 +829,9 @@
       <c r="G2" t="str">
         <v>0105101010555510101510101010510655101015201010101055555101010101010</v>
       </c>
+      <c r="H2" t="str">
+        <v>CNY</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
